--- a/02 Solution Architecture/design/EPMS Architectural Decisions V1.0 D.xlsx
+++ b/02 Solution Architecture/design/EPMS Architectural Decisions V1.0 D.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sougatabagchi/Projects/MSIL/Enterprise-PM-Platform/epms-2/02 Solution Architecture/design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E87A021-1317-2F41-B010-2826ACDCF7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82F01F6-68AB-5D4B-A94E-85F90F96AD59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="245">
   <si>
     <t>Key Decisions</t>
   </si>
@@ -861,6 +861,19 @@
   </si>
   <si>
     <t>Adopt adapter-based integration through secured APIs/events, with EPMS using dedicated integration services to connect external systems such as JIRA, SAP avoiding direct point-to-point coupling from core business services.</t>
+  </si>
+  <si>
+    <t>Workfflow implementation</t>
+  </si>
+  <si>
+    <t>Tool based workflow management
+Hard Coded flow management</t>
+  </si>
+  <si>
+    <t>Workflow management can be configurable using a tool. This adds flexibility but comes with additional complexity for configuring the flow.</t>
+  </si>
+  <si>
+    <t>Use workflow tool for configurable workflows. Not to use tool for configuration where flow is always fixed and simple (3-4 steps).</t>
   </si>
 </sst>
 </file>
@@ -1221,7 +1234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CD67CC2-0296-0541-92C5-18D86BEF4A34}">
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="26" style="7" customWidth="1"/>
@@ -1920,245 +1933,259 @@
         <v>152</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" ht="80" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B58" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C58" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="D57" s="5" t="s">
+      <c r="D58" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="100" x14ac:dyDescent="0.25">
-      <c r="A58" s="5" t="s">
+    <row r="59" spans="1:4" ht="100" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B59" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C59" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D58" s="5" t="s">
+      <c r="D59" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="340" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
+    <row r="60" spans="1:4" ht="340" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B60" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C60" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="D59" s="5" t="s">
+      <c r="D60" s="5" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="20" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
+    <row r="61" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-    </row>
-    <row r="61" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A61" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>113</v>
-      </c>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
     </row>
     <row r="62" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A63" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B63" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C63" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="D63" s="5" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="20" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
+    <row r="64" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-    </row>
-    <row r="64" spans="1:4" ht="80" x14ac:dyDescent="0.25">
-      <c r="A64" s="5" t="s">
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+    </row>
+    <row r="65" spans="1:4" ht="80" x14ac:dyDescent="0.25">
+      <c r="A65" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B65" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C65" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="D65" s="5" t="s">
         <v>148</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A65" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A67" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B67" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="C67" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="D66" s="5" t="s">
+      <c r="D67" s="5" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="20" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
+    <row r="68" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-    </row>
-    <row r="68" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A68" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>173</v>
-      </c>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
     </row>
     <row r="69" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A74" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="B74" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C73" s="5" t="s">
+      <c r="C74" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="D73" s="5" t="s">
+      <c r="D74" s="5" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="20" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
+    <row r="75" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-    </row>
-    <row r="75" spans="1:4" ht="100" x14ac:dyDescent="0.25">
-      <c r="A75" s="5" t="s">
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+    </row>
+    <row r="76" spans="1:4" ht="100" x14ac:dyDescent="0.25">
+      <c r="A76" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B75" s="5" t="s">
+      <c r="B76" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C75" s="5" t="s">
+      <c r="C76" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D75" s="5" t="s">
+      <c r="D76" s="5" t="s">
         <v>45</v>
       </c>
     </row>

--- a/02 Solution Architecture/design/EPMS Architectural Decisions V1.0 D.xlsx
+++ b/02 Solution Architecture/design/EPMS Architectural Decisions V1.0 D.xlsx
@@ -10,12 +10,25 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82F01F6-68AB-5D4B-A94E-85F90F96AD59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 

--- a/02 Solution Architecture/design/EPMS Architectural Decisions V1.0 D.xlsx
+++ b/02 Solution Architecture/design/EPMS Architectural Decisions V1.0 D.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sougatabagchi/Projects/MSIL/Enterprise-PM-Platform/epms-2/02 Solution Architecture/design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82F01F6-68AB-5D4B-A94E-85F90F96AD59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A600D179-2FFF-3041-8794-33EC02F71A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="265">
   <si>
     <t>Key Decisions</t>
   </si>
@@ -887,13 +887,79 @@
   </si>
   <si>
     <t>Use workflow tool for configurable workflows. Not to use tool for configuration where flow is always fixed and simple (3-4 steps).</t>
+  </si>
+  <si>
+    <t>Direct LLM APIsAWS BedrockHybrid (multi-provider)</t>
+  </si>
+  <si>
+    <t>Direct APIs give flexibility but increase integration overhead. Bedrock provides managed, secure, enterprise-grade access with built-in agents, guardrails, and RAG. Hybrid avoids vendor lock-in but adds complexity.</t>
+  </si>
+  <si>
+    <t>Embedding AI in services leads to duplication and governance issues. Central orchestration enables reuse, control, and consistency. Hybrid may increase complexity.</t>
+  </si>
+  <si>
+    <t>Generic assistants lack domain context. Persona-based agents align with business roles and improve usability, control, and explainability.</t>
+  </si>
+  <si>
+    <t>LLM-only responses may be inaccurate. RAG improves grounding, relevance, and enterprise trust. Adds complexity but is essential for enterprise use cases.</t>
+  </si>
+  <si>
+    <t>Fully autonomous AIManual-only approvalControlled AI with approval gates</t>
+  </si>
+  <si>
+    <t>Fully autonomous AI is risky. Manual-only reduces efficiency. Controlled AI ensures safety while enabling automation.</t>
+  </si>
+  <si>
+    <t>AI Platform Selection</t>
+  </si>
+  <si>
+    <t>AI Architecture Pattern</t>
+  </si>
+  <si>
+    <t>Agent Strategy (Persona-based AI)</t>
+  </si>
+  <si>
+    <t>Knowledge &amp; Retrieval Strategy (RAG)</t>
+  </si>
+  <si>
+    <t>Human-in-the-loop &amp; Governance</t>
+  </si>
+  <si>
+    <t>Use AWS Bedrock as primary AI platform, with abstraction layer to allow future multi-model flexibility.</t>
+  </si>
+  <si>
+    <t>Adopt centralized AI Orchestration layer for prompt, model, and agent management.</t>
+  </si>
+  <si>
+    <t>Implement persona-based modular agents (PM, Evaluator, Governance, Release Manager, etc.).</t>
+  </si>
+  <si>
+    <t>Use RAG-based knowledge layer (Bedrock Knowledge Base + vector store) for all enterprise AI responses.</t>
+  </si>
+  <si>
+    <t>Adopt human-in-the-loop model, where AI recommends/actions but critical decisions require approval.</t>
+  </si>
+  <si>
+    <t>Embed AI in each microservice 
+Centralized AI Orchestrator
+Hybrid</t>
+  </si>
+  <si>
+    <t>No agents (only GenAI APIs)
+Generic assistant
+Persona-based modular agents</t>
+  </si>
+  <si>
+    <t>No RAG (LLM only)
+External search
+RAG with vector DB / Bedrock KB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -927,6 +993,14 @@
       <b/>
       <sz val="14"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1023,7 +1097,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1053,6 +1127,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1247,13 +1322,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CD67CC2-0296-0541-92C5-18D86BEF4A34}">
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="26" style="7" customWidth="1"/>
     <col min="3" max="3" width="38.83203125" style="7" customWidth="1"/>
     <col min="4" max="4" width="35" style="7" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="1"/>
+    <col min="5" max="6" width="10.83203125" style="1"/>
+    <col min="7" max="7" width="33.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1378,7 +1455,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="100" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="120" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
@@ -1406,11 +1483,19 @@
         <v>240</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+    <row r="13" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:4" ht="20" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
@@ -1518,11 +1603,19 @@
         <v>232</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
+    <row r="22" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="23" spans="1:4" ht="20" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
@@ -1636,11 +1729,19 @@
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
+    <row r="32" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="33" spans="1:4" ht="20" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
@@ -1678,7 +1779,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="80" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>104</v>
       </c>
@@ -1720,7 +1821,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="80" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="100" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>29</v>
       </c>
@@ -1763,442 +1864,582 @@
       </c>
     </row>
     <row r="42" spans="1:4" ht="20" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-    </row>
-    <row r="43" spans="1:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+    </row>
+    <row r="44" spans="1:4" ht="120" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B44" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C44" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D44" s="5" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="100" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="100" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="100" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B46" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C46" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="D46" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="20" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
+    <row r="47" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-    </row>
-    <row r="47" spans="1:4" ht="100" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+    </row>
+    <row r="48" spans="1:4" ht="100" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B48" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C48" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="D48" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
+    <row r="49" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B49" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C49" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="D48" s="5" t="s">
+      <c r="D49" s="5" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="5"/>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-    </row>
     <row r="50" spans="1:4" ht="20" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-    </row>
-    <row r="51" spans="1:4" ht="80" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>89</v>
-      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
     </row>
     <row r="52" spans="1:4" ht="80" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>131</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="80" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="80" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B54" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C54" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="D54" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
+    <row r="55" spans="1:4" ht="120" x14ac:dyDescent="0.25">
+      <c r="A55" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B55" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C55" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D54" s="5" t="s">
+      <c r="D55" s="5" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A57" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B57" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C57" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="D57" s="5" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="80" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
+    <row r="58" spans="1:4" ht="80" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B58" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C58" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="D57" s="5" t="s">
+      <c r="D58" s="5" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A58" s="5" t="s">
+    <row r="59" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B59" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C59" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="D58" s="5" t="s">
+      <c r="D59" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="100" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
+    <row r="60" spans="1:4" ht="100" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B60" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C60" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D59" s="5" t="s">
+      <c r="D60" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="340" x14ac:dyDescent="0.25">
-      <c r="A60" s="5" t="s">
+    <row r="61" spans="1:4" ht="340" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B61" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="C61" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="D60" s="5" t="s">
+      <c r="D61" s="5" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="20" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
+    <row r="62" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-    </row>
-    <row r="62" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A62" s="5" t="s">
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+    </row>
+    <row r="64" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A64" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B64" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C64" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="D64" s="5" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A63" s="5" t="s">
+    <row r="65" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A65" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B65" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="C65" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="D65" s="5" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="20" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
+    <row r="66" spans="1:10" ht="20" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-    </row>
-    <row r="65" spans="1:4" ht="80" x14ac:dyDescent="0.25">
-      <c r="A65" s="5" t="s">
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+    </row>
+    <row r="67" spans="1:10" ht="80" x14ac:dyDescent="0.25">
+      <c r="A67" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="B67" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="C67" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D65" s="5" t="s">
+      <c r="D67" s="5" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A66" s="5" t="s">
+    <row r="68" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A68" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B68" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="C68" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D66" s="5" t="s">
+      <c r="D68" s="5" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A67" s="5" t="s">
+    <row r="69" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A69" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="B69" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="C69" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="D67" s="5" t="s">
+      <c r="D69" s="5" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="20" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
+    <row r="70" spans="1:10" ht="20" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="20" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-    </row>
-    <row r="69" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A69" s="5" t="s">
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="G71" s="11"/>
+      <c r="H71"/>
+      <c r="I71"/>
+      <c r="J71"/>
+    </row>
+    <row r="72" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A72" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="B72" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="C69" s="5" t="s">
+      <c r="C72" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="D69" s="5" t="s">
+      <c r="D72" s="5" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A70" s="5" t="s">
+      <c r="G72" s="11"/>
+      <c r="H72"/>
+      <c r="I72"/>
+      <c r="J72"/>
+    </row>
+    <row r="73" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A73" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="B73" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="C70" s="5" t="s">
+      <c r="C73" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="D70" s="5" t="s">
+      <c r="D73" s="5" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A71" s="5" t="s">
+      <c r="G73" s="11"/>
+      <c r="H73"/>
+      <c r="I73"/>
+      <c r="J73"/>
+    </row>
+    <row r="74" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A74" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="B74" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="C74" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D71" s="5" t="s">
+      <c r="D74" s="5" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A72" s="5" t="s">
+      <c r="G74" s="11"/>
+      <c r="H74"/>
+      <c r="I74"/>
+      <c r="J74"/>
+    </row>
+    <row r="75" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A75" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="B75" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="C72" s="5" t="s">
+      <c r="C75" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="D72" s="5" t="s">
+      <c r="D75" s="5" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A73" s="5" t="s">
+      <c r="G75" s="11"/>
+      <c r="H75"/>
+      <c r="I75"/>
+      <c r="J75"/>
+    </row>
+    <row r="76" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A76" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="B76" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C73" s="5" t="s">
+      <c r="C76" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="D73" s="5" t="s">
+      <c r="D76" s="5" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A74" s="5" t="s">
+    <row r="77" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A77" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B77" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="C77" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="D74" s="5" t="s">
+      <c r="D77" s="5" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="20" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
+    <row r="78" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="A78" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="100" x14ac:dyDescent="0.25">
+      <c r="A79" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="100" x14ac:dyDescent="0.25">
+      <c r="A80" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="100" x14ac:dyDescent="0.25">
+      <c r="A81" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="80" x14ac:dyDescent="0.25">
+      <c r="A82" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-    </row>
-    <row r="76" spans="1:4" ht="100" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+    </row>
+    <row r="84" spans="1:4" ht="100" x14ac:dyDescent="0.25">
+      <c r="A84" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B84" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C84" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D76" s="5" t="s">
+      <c r="D84" s="5" t="s">
         <v>45</v>
       </c>
     </row>
